--- a/public/trajectory_template.xlsx
+++ b/public/trajectory_template.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,22 +28,15 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="002E5090"/>
-      <sz val="14"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <color rgb="00666666"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
-      <sz val="11"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <sz val="13"/>
     </font>
     <font>
       <sz val="10"/>
@@ -67,7 +60,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E8F0FE"/>
+        <fgColor rgb="00E8F4FD"/>
       </patternFill>
     </fill>
   </fills>
@@ -91,21 +84,19 @@
   </cellStyleXfs>
   <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="1" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -474,128 +465,133 @@
   <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Шаблон инклинометрии для загрузки в DeAllsoft</t>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Zenith</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Azimuth</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>TVD</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Заполните данные начиная со строки 5. Строку 4 (пример) удалите перед загрузкой.</t>
-        </is>
+      <c r="A2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>MD
-Глубина по стволу, м</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>Zenith
-Зенитный угол, °</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>Azimuth
-Азимут, °</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>TVD
-Верт. глубина, м
-(необязательно)</t>
-        </is>
+      <c r="A3" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>99.97</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>0</v>
+      <c r="A4" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>199.24</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="B5" s="4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>45</v>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>50</v>
+      <c r="A5" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>150</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>493.86</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="B6" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>90</v>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>99.90000000000001</v>
+      <c r="A6" s="2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>180</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>978.15</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="n">
+      <c r="A7" s="2" t="n">
+        <v>1500</v>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="C7" s="3" t="n">
         <v>200</v>
       </c>
-      <c r="B7" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>120</v>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>199.5</v>
+      <c r="D7" s="3" t="n">
+        <v>1453.5</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="n">
-        <v>300</v>
-      </c>
-      <c r="B8" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>150</v>
-      </c>
-      <c r="D8" s="4" t="n">
-        <v>298.2</v>
+      <c r="A8" s="2" t="n">
+        <v>2000</v>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>210</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>1910.2</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -606,20 +602,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="70" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="72" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>Инструкция</t>
-        </is>
-      </c>
-      <c r="B1" s="6" t="inlineStr"/>
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Как заполнить шаблон инклинометрии</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr"/>
     </row>
     <row r="2">
       <c r="A2" s="6" t="inlineStr"/>
@@ -645,7 +641,7 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>Глубина по стволу (measured depth), м. Обязательный.</t>
+          <t>Глубина по стволу (Measured Depth), метры. Обязательный.</t>
         </is>
       </c>
     </row>
@@ -657,7 +653,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>Зенитный угол, ° (0°=вертикально). Обязательный.</t>
+          <t>Зенитный угол, градусы (0° = вертикально). Обязательный.</t>
         </is>
       </c>
     </row>
@@ -669,7 +665,7 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>Азимут, ° (0°=север, 90°=восток). Обязательный.</t>
+          <t>Азимут, градусы (0° = север, 90° = восток). Обязательный.</t>
         </is>
       </c>
     </row>
@@ -681,7 +677,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>Вертикальная глубина, м. Если не указан — рассчитается автоматически.</t>
+          <t>Вертикальная глубина, метры. Необязательный — рассчитается автоматически.</t>
         </is>
       </c>
     </row>
@@ -692,7 +688,7 @@
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>Требования:</t>
+          <t>Правила заполнения:</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr"/>
@@ -705,7 +701,7 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>Первая точка — устье (MD=0).</t>
+          <t>Заголовки MD, Zenith, Azimuth, TVD должны быть в ПЕРВОЙ строке.</t>
         </is>
       </c>
     </row>
@@ -717,7 +713,7 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>Точки по возрастанию MD.</t>
+          <t>Первая точка данных — устье скважины (MD = 0).</t>
         </is>
       </c>
     </row>
@@ -729,7 +725,7 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>Минимум 2 точки.</t>
+          <t>Точки идут по возрастанию MD.</t>
         </is>
       </c>
     </row>
@@ -741,7 +737,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>Формат: .xlsx или .xls</t>
+          <t>Минимум 2 точки (устье + забой).</t>
         </is>
       </c>
     </row>
@@ -753,7 +749,31 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>Заголовки: MD, Zenith/Зенит/Inc, Azimuth/Азимут/Azi, TVD</t>
+          <t>Десятичный разделитель: точка ИЛИ запятая (программа понимает оба).</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>6.</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>Удалите примерные данные (синие строки) и заполните своими.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>7.</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>Сохраните файл как .xlsx и загрузите в программу.</t>
         </is>
       </c>
     </row>
